--- a/lcoe/ethanol/bio_ethanol_lcoe/LCOE_BIOETHANOL_1.xlsx
+++ b/lcoe/ethanol/bio_ethanol_lcoe/LCOE_BIOETHANOL_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethanol/bio_ethanol_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE30B42-6513-D648-93F5-7E2520839135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582D6234-D575-904B-BEE4-A9755410C407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="23500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,6 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr lang="en-US"/>
               <a:t>None</a:t>
             </a:r>
           </a:p>
@@ -1161,7 +1160,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000000-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1640,7 +1639,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000001-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2119,7 +2118,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000002-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2598,7 +2597,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000003-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3077,7 +3076,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000004-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3556,7 +3555,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000005-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4037,7 +4036,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000006-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4518,7 +4517,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000007-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4999,7 +4998,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-E615-E74E-A4D9-568E3B6888AE}"/>
+              <c16:uniqueId val="{00000008-9FDA-CB4A-8A41-B96A87A6390D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5206,7 +5205,6 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr lang="en-US"/>
               <a:t>None</a:t>
             </a:r>
           </a:p>
@@ -5692,7 +5690,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-24D3-DA42-94EF-750F00848342}"/>
+              <c16:uniqueId val="{00000000-E449-5E4E-A9EA-9706C46F5F8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6617,43 +6615,43 @@
         <v>0</v>
       </c>
       <c r="AI4" s="1">
-        <f>M4/F4/(0.9*8760)</f>
+        <f t="shared" ref="AI4:AI35" si="8">M4/F4/(0.9*8760)</f>
         <v>17.45471442935871</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" ref="AJ4:AJ35" si="8">N4/F4/(0.9*8760)</f>
+        <f t="shared" ref="AJ4:AJ35" si="9">N4/F4/(0.9*8760)</f>
         <v>9.2063495350048488</v>
       </c>
       <c r="AK4" s="1">
-        <f t="shared" ref="AK4:AK35" si="9">O4/F4</f>
+        <f t="shared" ref="AK4:AK35" si="10">O4/F4</f>
         <v>0.22672309552599759</v>
       </c>
       <c r="AL4" s="1">
-        <f t="shared" ref="AL4:AL35" si="10">SUM(AZ4:BD4)-AW4</f>
+        <f t="shared" ref="AL4:AL35" si="11">SUM(AZ4:BD4)-AW4</f>
         <v>4.1928061038642994E-6</v>
       </c>
       <c r="AM4" s="1">
-        <f>(Q4+R4)*-1*(I4+K4)/F4</f>
+        <f t="shared" ref="AM4:AM35" si="12">(Q4+R4)*-1*(I4+K4)/F4</f>
         <v>0</v>
       </c>
       <c r="AN4" s="1">
-        <f t="shared" ref="AN4:AN35" si="11">AL4*Q4</f>
+        <f t="shared" ref="AN4:AN35" si="13">AL4*Q4</f>
         <v>4.6513101218559523E-4</v>
       </c>
       <c r="AO4" s="1">
-        <f t="shared" ref="AO4:AO35" si="12">SUM(AZ4:BB4)-AW4</f>
+        <f t="shared" ref="AO4:AO35" si="14">SUM(AZ4:BB4)-AW4</f>
         <v>4.1928061038642994E-6</v>
       </c>
       <c r="AP4" s="1">
-        <f t="shared" ref="AP4:AP35" si="13">(I4+K4)/F4*-1*R4</f>
+        <f t="shared" ref="AP4:AP35" si="15">(I4+K4)/F4*-1*R4</f>
         <v>0</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" ref="AQ4:AQ35" si="14">AO4*Q4</f>
+        <f t="shared" ref="AQ4:AQ35" si="16">AO4*Q4</f>
         <v>4.6513101218559523E-4</v>
       </c>
       <c r="AS4" s="9">
-        <f t="shared" ref="AS4:AS35" si="15">H4</f>
+        <f t="shared" ref="AS4:AS35" si="17">H4</f>
         <v>1.7230000000000001</v>
       </c>
       <c r="AT4" s="10">
@@ -6663,35 +6661,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW4" s="10">
-        <f t="shared" ref="AW4:AW35" si="16">AS4/F4</f>
+        <f t="shared" ref="AW4:AW35" si="18">AS4/F4</f>
         <v>0.86809754131398642</v>
       </c>
       <c r="AX4" s="10">
-        <f t="shared" ref="AX4:AX35" si="17">AT4*G4/F4</f>
+        <f t="shared" ref="AX4:AX35" si="19">AT4*G4/F4</f>
         <v>0</v>
       </c>
       <c r="AZ4" s="10">
-        <f t="shared" ref="AZ4:AZ35" si="18">AU4</f>
+        <f t="shared" ref="AZ4:AZ35" si="20">AU4</f>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA4" s="10">
-        <f>J4/F4</f>
+        <f t="shared" ref="BA4:BA35" si="21">J4/F4</f>
         <v>0.6377268241200903</v>
       </c>
       <c r="BB4" s="10">
-        <f>L4/F4</f>
+        <f t="shared" ref="BB4:BB35" si="22">L4/F4</f>
         <v>0</v>
       </c>
       <c r="BC4" s="10">
-        <f t="shared" ref="BC4:BC35" si="19">I4/F4</f>
+        <f t="shared" ref="BC4:BC35" si="23">I4/F4</f>
         <v>0</v>
       </c>
       <c r="BD4" s="10">
-        <f t="shared" ref="BD4:BD35" si="20">K4/F4</f>
+        <f t="shared" ref="BD4:BD35" si="24">K4/F4</f>
         <v>0</v>
       </c>
       <c r="BF4" s="1">
-        <f t="shared" ref="BF4:BF35" si="21">SUM(AW4:AX4)-SUM(AZ4:BD4)</f>
+        <f t="shared" ref="BF4:BF35" si="25">SUM(AW4:AX4)-SUM(AZ4:BD4)</f>
         <v>-4.1928061038642994E-6</v>
       </c>
     </row>
@@ -6799,43 +6797,43 @@
         <v>0</v>
       </c>
       <c r="AI5" s="1">
-        <f t="shared" ref="AI5:AI69" si="22">M5/F5/(0.9*8760)</f>
+        <f t="shared" si="8"/>
         <v>17.388133507022271</v>
       </c>
       <c r="AJ5" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.1712319599867627</v>
       </c>
       <c r="AK5" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22585826139329454</v>
       </c>
       <c r="AL5" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7318957232781429E-6</v>
       </c>
       <c r="AM5" s="1">
-        <f t="shared" ref="AM4:AM35" si="23">(Q5+R5)*-1*(I5+K5)/F5</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN5" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.9212870588645236E-4</v>
       </c>
       <c r="AO5" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1.7318957232781429E-6</v>
       </c>
       <c r="AP5" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ5" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.9212870588645236E-4</v>
       </c>
       <c r="AS5" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.736</v>
       </c>
       <c r="AT5" s="10">
@@ -6845,35 +6843,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW5" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.8713109817305762</v>
       </c>
       <c r="AX5" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ5" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA5" s="10">
-        <f t="shared" ref="BA4:BA35" si="24">J5/F5</f>
+        <f t="shared" si="21"/>
         <v>0.64093780362629948</v>
       </c>
       <c r="BB5" s="10">
-        <f t="shared" ref="BB4:BB35" si="25">L5/F5</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC5" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BD5" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>-1.7318957232781429E-6</v>
       </c>
     </row>
@@ -6981,43 +6979,43 @@
         <v>0</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.350687233631078</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.1514812225560309</v>
       </c>
       <c r="AK6" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22537186357489861</v>
       </c>
       <c r="AL6" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.6106847578775145E-6</v>
       </c>
       <c r="AM6" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-5.1148858668272773E-4</v>
       </c>
       <c r="AO6" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-4.6106847578775145E-6</v>
       </c>
       <c r="AP6" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ6" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-5.1148858668272773E-4</v>
       </c>
       <c r="AS6" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.74</v>
       </c>
       <c r="AT6" s="10">
@@ -7027,35 +7025,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW6" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87143787248960791</v>
       </c>
       <c r="AX6" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ6" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA6" s="10">
+        <f t="shared" si="21"/>
+        <v>0.64105835180485005</v>
+      </c>
+      <c r="BB6" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD6" s="10">
         <f t="shared" si="24"/>
-        <v>0.64105835180485005</v>
-      </c>
-      <c r="BB6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD6" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF6" s="1">
-        <f t="shared" si="21"/>
         <v>4.6106847578775145E-6</v>
       </c>
     </row>
@@ -7163,43 +7161,43 @@
         <v>0</v>
       </c>
       <c r="AI7" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.483783597976871</v>
       </c>
       <c r="AJ7" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.2216818355173462</v>
       </c>
       <c r="AK7" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22710068130204392</v>
       </c>
       <c r="AL7" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7067917074408143E-7</v>
       </c>
       <c r="AM7" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN7" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.0027927251325848E-5</v>
       </c>
       <c r="AO7" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2.7067917074408143E-7</v>
       </c>
       <c r="AP7" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>3.0027927251325848E-5</v>
       </c>
       <c r="AS7" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7170000000000001</v>
       </c>
       <c r="AT7" s="10">
@@ -7209,35 +7207,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW7" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86651526621246533</v>
       </c>
       <c r="AX7" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ7" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA7" s="10">
+        <f t="shared" si="21"/>
+        <v>0.63614062689163609</v>
+      </c>
+      <c r="BB7" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD7" s="10">
         <f t="shared" si="24"/>
-        <v>0.63614062689163609</v>
-      </c>
-      <c r="BB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD7" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF7" s="1">
-        <f t="shared" si="21"/>
         <v>-2.7067917074408143E-7</v>
       </c>
     </row>
@@ -7345,43 +7343,43 @@
         <v>0</v>
       </c>
       <c r="AI8" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.531560750666046</v>
       </c>
       <c r="AJ8" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.2468815126145572</v>
       </c>
       <c r="AK8" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22772126916654017</v>
       </c>
       <c r="AL8" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.3630672258719869E-6</v>
       </c>
       <c r="AM8" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN8" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.949545066942512E-4</v>
       </c>
       <c r="AO8" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.3630672258719869E-6</v>
       </c>
       <c r="AP8" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ8" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5.949545066942512E-4</v>
       </c>
       <c r="AS8" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.714</v>
       </c>
       <c r="AT8" s="10">
@@ -7391,35 +7389,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW8" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86736501189211068</v>
       </c>
       <c r="AX8" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ8" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA8" s="10">
+        <f t="shared" si="21"/>
+        <v>0.63699546495933657</v>
+      </c>
+      <c r="BB8" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC8" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD8" s="10">
         <f t="shared" si="24"/>
-        <v>0.63699546495933657</v>
-      </c>
-      <c r="BB8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD8" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF8" s="1">
-        <f t="shared" si="21"/>
         <v>-5.3630672258719869E-6</v>
       </c>
     </row>
@@ -7527,43 +7525,43 @@
         <v>0</v>
       </c>
       <c r="AI9" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>16.686310181770139</v>
       </c>
       <c r="AJ9" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.8010608597811508</v>
       </c>
       <c r="AK9" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.2167421250361237</v>
       </c>
       <c r="AL9" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.9546125806790826E-6</v>
       </c>
       <c r="AM9" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN9" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-2.168359102616363E-4</v>
       </c>
       <c r="AO9" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.9546125806790826E-6</v>
       </c>
       <c r="AP9" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-2.168359102616363E-4</v>
       </c>
       <c r="AS9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.802</v>
       </c>
       <c r="AT9" s="10">
@@ -7573,35 +7571,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW9" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86793179847798863</v>
       </c>
       <c r="AX9" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ9" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA9" s="10">
+        <f t="shared" si="21"/>
+        <v>0.63755493386540796</v>
+      </c>
+      <c r="BB9" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC9" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD9" s="10">
         <f t="shared" si="24"/>
-        <v>0.63755493386540796</v>
-      </c>
-      <c r="BB9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC9" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD9" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF9" s="1">
-        <f t="shared" si="21"/>
         <v>1.9546125806790826E-6</v>
       </c>
     </row>
@@ -7709,43 +7707,43 @@
         <v>0</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>16.738714402759417</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.8287010470491492</v>
       </c>
       <c r="AK10" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21742281490071025</v>
       </c>
       <c r="AL10" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6467424278632237E-6</v>
       </c>
       <c r="AM10" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN10" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8268218307902363E-4</v>
       </c>
       <c r="AO10" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1.6467424278632237E-6</v>
       </c>
       <c r="AP10" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.8268218307902363E-4</v>
       </c>
       <c r="AS10" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.806</v>
       </c>
       <c r="AT10" s="10">
@@ -7755,35 +7753,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW10" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87259023046818374</v>
       </c>
       <c r="AX10" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ10" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA10" s="10">
+        <f t="shared" si="21"/>
+        <v>0.64221696721061161</v>
+      </c>
+      <c r="BB10" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC10" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="10">
         <f t="shared" si="24"/>
-        <v>0.64221696721061161</v>
-      </c>
-      <c r="BB10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF10" s="1">
-        <f t="shared" si="21"/>
         <v>-1.6467424278632237E-6</v>
       </c>
     </row>
@@ -7891,43 +7889,43 @@
         <v>0</v>
       </c>
       <c r="AI11" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>16.695155510284405</v>
       </c>
       <c r="AJ11" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.8057262575671658</v>
       </c>
       <c r="AK11" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21685701893884632</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-3.2062761148310415E-6</v>
       </c>
       <c r="AM11" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-3.5568982149290616E-4</v>
       </c>
       <c r="AO11" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-3.2062761148310415E-6</v>
       </c>
       <c r="AP11" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-3.5568982149290616E-4</v>
       </c>
       <c r="AS11" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.802</v>
       </c>
       <c r="AT11" s="10">
@@ -7937,35 +7935,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW11" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86839188472844686</v>
       </c>
       <c r="AX11" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ11" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA11" s="10">
+        <f t="shared" si="21"/>
+        <v>0.63801376845233204</v>
+      </c>
+      <c r="BB11" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC11" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="10">
         <f t="shared" si="24"/>
-        <v>0.63801376845233204</v>
-      </c>
-      <c r="BB11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF11" s="1">
-        <f t="shared" si="21"/>
         <v>3.2062761148310415E-6</v>
       </c>
     </row>
@@ -8073,43 +8071,43 @@
         <v>0</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>16.625452154425169</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.7689617799585484</v>
       </c>
       <c r="AK12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21595162683558883</v>
       </c>
       <c r="AL12" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.2851613186734028E-6</v>
       </c>
       <c r="AM12" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN12" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-4.7537648347156401E-4</v>
       </c>
       <c r="AO12" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-4.2851613186734028E-6</v>
       </c>
       <c r="AP12" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ12" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-4.7537648347156401E-4</v>
       </c>
       <c r="AS12" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.821</v>
       </c>
       <c r="AT12" s="10">
@@ -8119,35 +8117,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW12" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87388424992801605</v>
       </c>
       <c r="AX12" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ12" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA12" s="10">
+        <f t="shared" si="21"/>
+        <v>0.64350505476669739</v>
+      </c>
+      <c r="BB12" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC12" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD12" s="10">
         <f t="shared" si="24"/>
-        <v>0.64350505476669739</v>
-      </c>
-      <c r="BB12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD12" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF12" s="1">
-        <f t="shared" si="21"/>
         <v>4.2851613186734028E-6</v>
       </c>
     </row>
@@ -8255,43 +8253,43 @@
         <v>0</v>
       </c>
       <c r="AI13" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>16.836330465758454</v>
       </c>
       <c r="AJ13" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8.8801878588120839</v>
       </c>
       <c r="AK13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21869077124945327</v>
       </c>
       <c r="AL13" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.0211364076528895E-6</v>
       </c>
       <c r="AM13" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN13" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.1328027080322227E-4</v>
       </c>
       <c r="AO13" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.0211364076528895E-6</v>
       </c>
       <c r="AP13" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ13" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-1.1328027080322227E-4</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.821</v>
       </c>
       <c r="AT13" s="10">
@@ -8301,35 +8299,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW13" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.88496865432278748</v>
       </c>
       <c r="AX13" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ13" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA13" s="10">
+        <f t="shared" si="21"/>
+        <v>0.65459272318637984</v>
+      </c>
+      <c r="BB13" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC13" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD13" s="10">
         <f t="shared" si="24"/>
-        <v>0.65459272318637984</v>
-      </c>
-      <c r="BB13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC13" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD13" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF13" s="1">
-        <f t="shared" si="21"/>
         <v>1.0211364076528895E-6</v>
       </c>
     </row>
@@ -8437,43 +8435,43 @@
         <v>0</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.5322120463203</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.7746670359888874</v>
       </c>
       <c r="AK14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24071894725580401</v>
       </c>
       <c r="AL14" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.1797471771752868E-6</v>
       </c>
       <c r="AM14" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN14" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.7461780671529876E-4</v>
       </c>
       <c r="AO14" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.1797471771752868E-6</v>
       </c>
       <c r="AP14" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5.7461780671529876E-4</v>
       </c>
       <c r="AS14" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7</v>
       </c>
       <c r="AT14" s="10">
@@ -8483,35 +8481,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW14" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90938268963303737</v>
       </c>
       <c r="AX14" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ14" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA14" s="10">
+        <f t="shared" si="21"/>
+        <v>0.67901295938021455</v>
+      </c>
+      <c r="BB14" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC14" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD14" s="10">
         <f t="shared" si="24"/>
-        <v>0.67901295938021455</v>
-      </c>
-      <c r="BB14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC14" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD14" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF14" s="1">
-        <f t="shared" si="21"/>
         <v>-5.1797471771752868E-6</v>
       </c>
     </row>
@@ -8619,43 +8617,43 @@
         <v>0</v>
       </c>
       <c r="AI15" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.41498814617082</v>
       </c>
       <c r="AJ15" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.7128382273309022</v>
       </c>
       <c r="AK15" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23919630043055334</v>
       </c>
       <c r="AL15" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.1699975755760121E-6</v>
       </c>
       <c r="AM15" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-4.6260073685532965E-4</v>
       </c>
       <c r="AO15" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-4.1699975755760121E-6</v>
       </c>
       <c r="AP15" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ15" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-4.6260073685532965E-4</v>
       </c>
       <c r="AS15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.708</v>
       </c>
       <c r="AT15" s="10">
@@ -8665,35 +8663,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW15" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90788284696752242</v>
       </c>
       <c r="AX15" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ15" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA15" s="10">
+        <f t="shared" si="21"/>
+        <v>0.67750376696994685</v>
+      </c>
+      <c r="BB15" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC15" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD15" s="10">
         <f t="shared" si="24"/>
-        <v>0.67750376696994685</v>
-      </c>
-      <c r="BB15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC15" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD15" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF15" s="1">
-        <f t="shared" si="21"/>
         <v>4.1699975755760121E-6</v>
       </c>
     </row>
@@ -8801,43 +8799,43 @@
         <v>0</v>
       </c>
       <c r="AI16" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.393478736071767</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.7014932609915725</v>
       </c>
       <c r="AK16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23891691000796392</v>
       </c>
       <c r="AL16" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.4094306270973078E-6</v>
       </c>
       <c r="AM16" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN16" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.56355881466339E-4</v>
       </c>
       <c r="AO16" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.4094306270973078E-6</v>
       </c>
       <c r="AP16" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-1.56355881466339E-4</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.71</v>
       </c>
       <c r="AT16" s="10">
@@ -8847,35 +8845,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW16" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90788425803026285</v>
       </c>
       <c r="AX16" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ16" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA16" s="10">
+        <f t="shared" si="21"/>
+        <v>0.67750793859963576</v>
+      </c>
+      <c r="BB16" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC16" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD16" s="10">
         <f t="shared" si="24"/>
-        <v>0.67750793859963576</v>
-      </c>
-      <c r="BB16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC16" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD16" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF16" s="1">
-        <f t="shared" si="21"/>
         <v>1.4094306270973078E-6</v>
       </c>
     </row>
@@ -8983,43 +8981,43 @@
         <v>0</v>
       </c>
       <c r="AI17" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.467997867365622</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.7407977808399302</v>
       </c>
       <c r="AK17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23988485526947068</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1816141211040687E-6</v>
       </c>
       <c r="AM17" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN17" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.3108294506044156E-4</v>
       </c>
       <c r="AO17" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1.1816141211040687E-6</v>
       </c>
       <c r="AP17" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ17" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.3108294506044156E-4</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.6890000000000001</v>
       </c>
       <c r="AT17" s="10">
@@ -9029,35 +9027,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW17" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90036782344474664</v>
       </c>
       <c r="AX17" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ17" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA17" s="10">
+        <f t="shared" si="21"/>
+        <v>0.66999409505886776</v>
+      </c>
+      <c r="BB17" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC17" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD17" s="10">
         <f t="shared" si="24"/>
-        <v>0.66999409505886776</v>
-      </c>
-      <c r="BB17" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC17" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD17" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF17" s="1">
-        <f t="shared" si="21"/>
         <v>-1.1816141211040687E-6</v>
       </c>
     </row>
@@ -9165,43 +9163,43 @@
         <v>0</v>
       </c>
       <c r="AI18" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>19.18066504229386</v>
       </c>
       <c r="AJ18" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.11668838283558</v>
       </c>
       <c r="AK18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24914184475694828</v>
       </c>
       <c r="AL18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.4462940705062266E-6</v>
       </c>
       <c r="AM18" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.60445345734585E-4</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.4462940705062266E-6</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-1.60445345734585E-4</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.633</v>
       </c>
       <c r="AT18" s="10">
@@ -9211,35 +9209,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW18" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90410807219577016</v>
       </c>
       <c r="AX18" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ18" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA18" s="10">
+        <f t="shared" si="21"/>
+        <v>0.67373171590169967</v>
+      </c>
+      <c r="BB18" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC18" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BD18" s="10">
         <f t="shared" si="24"/>
-        <v>0.67373171590169967</v>
-      </c>
-      <c r="BB18" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC18" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="BD18" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF18" s="1">
-        <f t="shared" si="21"/>
         <v>1.4462940705062266E-6</v>
       </c>
     </row>
@@ -9347,43 +9345,43 @@
         <v>0</v>
       </c>
       <c r="AI19" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.725964591166843</v>
       </c>
       <c r="AJ19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.9021474929402586</v>
       </c>
       <c r="AK19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.2418379685610641</v>
       </c>
       <c r="AL19" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.1926591990426587E-6</v>
       </c>
       <c r="AM19" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-10.345201343073484</v>
       </c>
       <c r="AN19" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4.6511471522678245E-4</v>
       </c>
       <c r="AO19" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13055124274459151</v>
       </c>
       <c r="AP19" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>4.138030247275676</v>
       </c>
       <c r="AQ19" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.482766475633932</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7230000000000001</v>
       </c>
       <c r="AT19" s="10">
@@ -9393,35 +9391,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW19" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86809754131398642</v>
       </c>
       <c r="AX19" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ19" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA19" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50717138856939492</v>
+      </c>
+      <c r="BB19" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC19" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13055543540379055</v>
+      </c>
+      <c r="BD19" s="10">
         <f t="shared" si="24"/>
-        <v>0.50717138856939492</v>
-      </c>
-      <c r="BB19" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC19" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13055543540379055</v>
-      </c>
-      <c r="BD19" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF19" s="1">
-        <f t="shared" si="21"/>
         <v>-4.1926591990426587E-6</v>
       </c>
     </row>
@@ -9529,43 +9527,43 @@
         <v>0</v>
       </c>
       <c r="AI20" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.654534491341071</v>
       </c>
       <c r="AJ20" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.8643758000340416</v>
       </c>
       <c r="AK20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24091547881951414</v>
       </c>
       <c r="AL20" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.73174881690219E-6</v>
       </c>
       <c r="AM20" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-7.4022566740589788</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.9211240875521116E-4</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13121105537948452</v>
       </c>
       <c r="AP20" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>7.1538985539231899</v>
       </c>
       <c r="AQ20" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.555963115573416</v>
       </c>
       <c r="AS20" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.736</v>
       </c>
       <c r="AT20" s="10">
@@ -9575,35 +9573,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW20" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.8713109817305762</v>
       </c>
       <c r="AX20" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ20" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA20" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50972501635109169</v>
+      </c>
+      <c r="BB20" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC20" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13121278712830139</v>
+      </c>
+      <c r="BD20" s="10">
         <f t="shared" si="24"/>
-        <v>0.50972501635109169</v>
-      </c>
-      <c r="BB20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13121278712830139</v>
-      </c>
-      <c r="BD20" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF20" s="1">
-        <f t="shared" si="21"/>
         <v>-1.73174881690219E-6</v>
       </c>
     </row>
@@ -9711,43 +9709,43 @@
         <v>0</v>
       </c>
       <c r="AI21" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.614360955851129</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.8431323403554991</v>
       </c>
       <c r="AK21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24039665447989184</v>
       </c>
       <c r="AL21" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.6108316682502704E-6</v>
       </c>
       <c r="AM21" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-9.0852366732822762</v>
       </c>
       <c r="AN21" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-5.1150488425735611E-4</v>
       </c>
       <c r="AO21" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13124207658308173</v>
       </c>
       <c r="AP21" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5.473656289921391</v>
       </c>
       <c r="AQ21" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.559404468087926</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.74</v>
       </c>
       <c r="AT21" s="10">
@@ -9757,35 +9755,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW21" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87143787248960791</v>
       </c>
       <c r="AX21" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ21" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA21" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50982088590652619</v>
+      </c>
+      <c r="BB21" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC21" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13123746575141346</v>
+      </c>
+      <c r="BD21" s="10">
         <f t="shared" si="24"/>
-        <v>0.50982088590652619</v>
-      </c>
-      <c r="BB21" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC21" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13123746575141346</v>
-      </c>
-      <c r="BD21" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF21" s="1">
-        <f t="shared" si="21"/>
         <v>4.6108316682502704E-6</v>
       </c>
     </row>
@@ -9893,43 +9891,43 @@
         <v>0</v>
       </c>
       <c r="AI22" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.757150906155914</v>
       </c>
       <c r="AJ22" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.9186385788482578</v>
       </c>
       <c r="AK22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24224072672218017</v>
       </c>
       <c r="AL22" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7053226347995007E-7</v>
       </c>
       <c r="AM22" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-8.2407285226581717</v>
       </c>
       <c r="AN22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.0011630021554154E-5</v>
       </c>
       <c r="AO22" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13023043857491745</v>
       </c>
       <c r="AP22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>6.2064793958865287</v>
       </c>
       <c r="AQ22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.447177906914684</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7170000000000001</v>
       </c>
       <c r="AT22" s="10">
@@ -9939,35 +9937,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW22" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86651526621246533</v>
       </c>
       <c r="AX22" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ22" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA22" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50590991763754789</v>
+      </c>
+      <c r="BB22" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC22" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13023070910718088</v>
+      </c>
+      <c r="BD22" s="10">
         <f t="shared" si="24"/>
-        <v>0.50590991763754789</v>
-      </c>
-      <c r="BB22" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13023070910718088</v>
-      </c>
-      <c r="BD22" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF22" s="1">
-        <f t="shared" si="21"/>
         <v>-2.7053226347995007E-7</v>
       </c>
     </row>
@@ -10075,43 +10073,43 @@
         <v>0</v>
       </c>
       <c r="AI23" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>18.808407732679495</v>
       </c>
       <c r="AJ23" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.945742798435214</v>
       </c>
       <c r="AK23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.24290268711097615</v>
       </c>
       <c r="AL23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.3629203221605692E-6</v>
       </c>
       <c r="AM23" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-11.662990256654918</v>
       </c>
       <c r="AN23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.9493820985860157E-4</v>
       </c>
       <c r="AO23" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13040034863607908</v>
       </c>
       <c r="AP23" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.8036316448702485</v>
       </c>
       <c r="AQ23" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.46602696331531</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.714</v>
       </c>
       <c r="AT23" s="10">
@@ -10121,35 +10119,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW23" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86736501189211068</v>
       </c>
       <c r="AX23" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ23" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA23" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50658975325603162</v>
+      </c>
+      <c r="BB23" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC23" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13040571155640124</v>
+      </c>
+      <c r="BD23" s="10">
         <f t="shared" si="24"/>
-        <v>0.50658975325603162</v>
-      </c>
-      <c r="BB23" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC23" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13040571155640124</v>
-      </c>
-      <c r="BD23" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF23" s="1">
-        <f t="shared" si="21"/>
         <v>-5.3629203221605692E-6</v>
       </c>
     </row>
@@ -10257,43 +10255,43 @@
         <v>0</v>
       </c>
       <c r="AI24" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.901596436060082</v>
       </c>
       <c r="AJ24" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.4662278894074863</v>
       </c>
       <c r="AK24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23119160003853192</v>
       </c>
       <c r="AL24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.9547594888313924E-6</v>
       </c>
       <c r="AM24" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-10.34241294022325</v>
       </c>
       <c r="AN24" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-2.168522075899385E-4</v>
       </c>
       <c r="AO24" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13052220079034005</v>
       </c>
       <c r="AP24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>4.1369148996905283</v>
       </c>
       <c r="AQ24" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.479544692121362</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.802</v>
       </c>
       <c r="AT24" s="10">
@@ -10303,35 +10301,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW24" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86793179847798863</v>
       </c>
       <c r="AX24" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ24" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA24" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50703468768764859</v>
+      </c>
+      <c r="BB24" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC24" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13052024603085124</v>
+      </c>
+      <c r="BD24" s="10">
         <f t="shared" si="24"/>
-        <v>0.50703468768764859</v>
-      </c>
-      <c r="BB24" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF24" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13052024603085124</v>
-      </c>
-      <c r="BD24" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF24" s="1">
-        <f t="shared" si="21"/>
         <v>1.9547594888313924E-6</v>
       </c>
     </row>
@@ -10439,43 +10437,43 @@
         <v>0</v>
       </c>
       <c r="AI25" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.957817326447284</v>
       </c>
       <c r="AJ25" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.4959570681682486</v>
       </c>
       <c r="AK25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23191766922742424</v>
       </c>
       <c r="AL25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6465955217093153E-6</v>
       </c>
       <c r="AM25" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-7.4170298659783613</v>
       </c>
       <c r="AN25" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.826658859724151E-4</v>
       </c>
       <c r="AO25" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13147301090176011</v>
       </c>
       <c r="AP25" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>7.16817608048874</v>
       </c>
       <c r="AQ25" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.585023280581131</v>
       </c>
       <c r="AS25" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.806</v>
       </c>
       <c r="AT25" s="10">
@@ -10485,35 +10483,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87259023046818374</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA25" s="10">
+        <f t="shared" si="21"/>
+        <v>0.51074230956642364</v>
+      </c>
+      <c r="BB25" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC25" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13147465749728179</v>
+      </c>
+      <c r="BD25" s="10">
         <f t="shared" si="24"/>
-        <v>0.51074230956642364</v>
-      </c>
-      <c r="BB25" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF25" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC25" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13147465749728179</v>
-      </c>
-      <c r="BD25" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF25" s="1">
-        <f t="shared" si="21"/>
         <v>-1.6465955217093153E-6</v>
       </c>
     </row>
@@ -10621,43 +10619,43 @@
         <v>0</v>
       </c>
       <c r="AI26" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.911085981662545</v>
       </c>
       <c r="AJ26" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.4712458888669584</v>
       </c>
       <c r="AK26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23131415353476942</v>
       </c>
       <c r="AL26" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-3.2064230242045966E-6</v>
       </c>
       <c r="AM26" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-9.0420880889800586</v>
       </c>
       <c r="AN26" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-3.5570611895668783E-4</v>
       </c>
       <c r="AO26" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13061738507051035</v>
       </c>
       <c r="AP26" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5.4476602120688904</v>
       </c>
       <c r="AQ26" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.490104007167904</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.802</v>
       </c>
       <c r="AT26" s="10">
@@ -10667,35 +10665,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86839188472844686</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA26" s="10">
+        <f t="shared" si="21"/>
+        <v>0.50739958965793652</v>
+      </c>
+      <c r="BB26" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC26" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13061417864748615</v>
+      </c>
+      <c r="BD26" s="10">
         <f t="shared" si="24"/>
-        <v>0.50739958965793652</v>
-      </c>
-      <c r="BB26" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF26" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC26" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13061417864748615</v>
-      </c>
-      <c r="BD26" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF26" s="1">
-        <f t="shared" si="21"/>
         <v>3.2064230242045966E-6</v>
       </c>
     </row>
@@ -10803,43 +10801,43 @@
         <v>0</v>
       </c>
       <c r="AI27" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>17.836306037310653</v>
       </c>
       <c r="AJ27" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.4317028236816505</v>
       </c>
       <c r="AK27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23034840195796139</v>
       </c>
       <c r="AL27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.2853082289351363E-6</v>
       </c>
       <c r="AM27" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-8.3361292065503623</v>
       </c>
       <c r="AN27" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-4.7539278103387618E-4</v>
       </c>
       <c r="AO27" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13174264008999181</v>
       </c>
       <c r="AP27" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>6.2783301281734092</v>
       </c>
       <c r="AQ27" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.614934727504805</v>
       </c>
       <c r="AS27" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.821</v>
       </c>
       <c r="AT27" s="10">
@@ -10849,35 +10847,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.87388424992801605</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ27" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA27" s="10">
+        <f t="shared" si="21"/>
+        <v>0.51176669983802425</v>
+      </c>
+      <c r="BB27" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC27" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13173835478176288</v>
+      </c>
+      <c r="BD27" s="10">
         <f t="shared" si="24"/>
-        <v>0.51176669983802425</v>
-      </c>
-      <c r="BB27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF27" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC27" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13173835478176288</v>
-      </c>
-      <c r="BD27" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF27" s="1">
-        <f t="shared" si="21"/>
         <v>4.2853082289351363E-6</v>
       </c>
     </row>
@@ -10984,44 +10982,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI28">
+        <f t="shared" si="8"/>
         <v>18.062542897676021</v>
       </c>
       <c r="AJ28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.551335152834632</v>
       </c>
       <c r="AK28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23327015599941681</v>
       </c>
       <c r="AL28" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.021283315694177E-6</v>
       </c>
       <c r="AM28" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-11.985185095681334</v>
       </c>
       <c r="AN28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.1329656811920815E-4</v>
       </c>
       <c r="AO28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13400924354395638</v>
       </c>
       <c r="AP28" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.8810831068564151</v>
       </c>
       <c r="AQ28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-14.866381499105868</v>
       </c>
       <c r="AS28" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.821</v>
       </c>
       <c r="AT28" s="10">
@@ -11031,35 +11029,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW28" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.88496865432278748</v>
       </c>
       <c r="AX28" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ28" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA28" s="10">
+        <f t="shared" si="21"/>
+        <v>0.52058450077883112</v>
+      </c>
+      <c r="BB28" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC28" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13400822226064071</v>
+      </c>
+      <c r="BD28" s="10">
         <f t="shared" si="24"/>
-        <v>0.52058450077883112</v>
-      </c>
-      <c r="BB28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF28" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC28" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13400822226064071</v>
-      </c>
-      <c r="BD28" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF28" s="1">
-        <f t="shared" si="21"/>
         <v>1.021283315694177E-6</v>
       </c>
     </row>
@@ -11166,44 +11164,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI29">
+        <f t="shared" si="8"/>
         <v>19.881937798517143</v>
       </c>
       <c r="AJ29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.513417323198794</v>
       </c>
       <c r="AK29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25676687707285761</v>
       </c>
       <c r="AL29" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.1796002730197799E-6</v>
       </c>
       <c r="AM29" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-11.014944822393266</v>
       </c>
       <c r="AN29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.7460150983038385E-4</v>
       </c>
       <c r="AO29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13900235341397027</v>
       </c>
       <c r="AP29" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>4.4059243832555897</v>
       </c>
       <c r="AQ29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-15.420294604139023</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7</v>
       </c>
       <c r="AT29" s="10">
@@ -11213,35 +11211,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW29" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90938268963303737</v>
       </c>
       <c r="AX29" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ29" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA29" s="10">
+        <f t="shared" si="21"/>
+        <v>0.54000542621906711</v>
+      </c>
+      <c r="BB29" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC29" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13900753301424329</v>
+      </c>
+      <c r="BD29" s="10">
         <f t="shared" si="24"/>
-        <v>0.54000542621906711</v>
-      </c>
-      <c r="BB29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF29" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC29" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13900753301424329</v>
-      </c>
-      <c r="BD29" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF29" s="1">
-        <f t="shared" si="21"/>
         <v>-5.1796002730197799E-6</v>
       </c>
     </row>
@@ -11348,44 +11346,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI30">
+        <f t="shared" si="8"/>
         <v>19.756176325172991</v>
       </c>
       <c r="AJ30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.446915613664926</v>
       </c>
       <c r="AK30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.2551427204592569</v>
       </c>
       <c r="AL30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-4.1701444852826342E-6</v>
       </c>
       <c r="AM30" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-7.8245607490168307</v>
       </c>
       <c r="AN30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-4.6261703435606023E-4</v>
       </c>
       <c r="AO30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13870274128849736</v>
       </c>
       <c r="AP30" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>7.5620336192397284</v>
       </c>
       <c r="AQ30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-15.387056985290908</v>
       </c>
       <c r="AS30" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.708</v>
       </c>
       <c r="AT30" s="10">
@@ -11395,35 +11393,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW30" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90788284696752242</v>
       </c>
       <c r="AX30" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ30" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA30" s="10">
+        <f t="shared" si="21"/>
+        <v>0.53880519567902507</v>
+      </c>
+      <c r="BB30" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC30" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13869857114401213</v>
+      </c>
+      <c r="BD30" s="10">
         <f t="shared" si="24"/>
-        <v>0.53880519567902507</v>
-      </c>
-      <c r="BB30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF30" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC30" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13869857114401213</v>
-      </c>
-      <c r="BD30" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF30" s="1">
-        <f t="shared" si="21"/>
         <v>4.1701444852826342E-6</v>
       </c>
     </row>
@@ -11530,44 +11528,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI31" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI31">
+        <f t="shared" si="8"/>
         <v>19.733100356011654</v>
       </c>
       <c r="AJ31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.434713216876997</v>
       </c>
       <c r="AK31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25484470400849479</v>
       </c>
       <c r="AL31" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.4095775351385953E-6</v>
       </c>
       <c r="AM31" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-9.6018091846886779</v>
       </c>
       <c r="AN31">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.5637217878232488E-4</v>
       </c>
       <c r="AO31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13870083473757744</v>
       </c>
       <c r="AP31" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5.7848799242572264</v>
       </c>
       <c r="AQ31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-15.386845481124677</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.71</v>
       </c>
       <c r="AT31" s="10">
@@ -11577,35 +11575,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW31" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90788425803026285</v>
       </c>
       <c r="AX31" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ31" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA31" s="10">
+        <f t="shared" si="21"/>
+        <v>0.53880851329268542</v>
+      </c>
+      <c r="BB31" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC31" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13869942516004236</v>
+      </c>
+      <c r="BD31" s="10">
         <f t="shared" si="24"/>
-        <v>0.53880851329268542</v>
-      </c>
-      <c r="BB31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF31" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13869942516004236</v>
-      </c>
-      <c r="BD31" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF31" s="1">
-        <f t="shared" si="21"/>
         <v>1.4095775351385953E-6</v>
       </c>
     </row>
@@ -11712,44 +11710,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI32" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI32">
+        <f t="shared" si="8"/>
         <v>19.813046815154298</v>
       </c>
       <c r="AJ32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.476988295744883</v>
       </c>
       <c r="AK32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25587717895410206</v>
       </c>
       <c r="AL32" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1814672147281158E-6</v>
       </c>
       <c r="AM32" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-8.6792750153483205</v>
       </c>
       <c r="AN32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.3106664792920039E-4</v>
       </c>
       <c r="AO32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.137160009643162</v>
       </c>
       <c r="AP32" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>6.5367693409485392</v>
       </c>
       <c r="AQ32">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-15.215913289648929</v>
       </c>
       <c r="AS32" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.6890000000000001</v>
       </c>
       <c r="AT32" s="10">
@@ -11759,35 +11757,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW32" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90036782344474664</v>
       </c>
       <c r="AX32" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ32" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA32" s="10">
+        <f t="shared" si="21"/>
+        <v>0.53283290380158466</v>
+      </c>
+      <c r="BB32" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC32" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13716119111037672</v>
+      </c>
+      <c r="BD32" s="10">
         <f t="shared" si="24"/>
-        <v>0.53283290380158466</v>
-      </c>
-      <c r="BB32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF32" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13716119111037672</v>
-      </c>
-      <c r="BD32" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF32" s="1">
-        <f t="shared" si="21"/>
         <v>-1.1814672147281158E-6</v>
       </c>
     </row>
@@ -11894,44 +11892,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI33" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI33">
+        <f t="shared" si="8"/>
         <v>20.577618492164735</v>
       </c>
       <c r="AJ33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10.881287976961479</v>
       </c>
       <c r="AK33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.26575130107407818</v>
       </c>
       <c r="AL33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1.4464409785475141E-6</v>
       </c>
       <c r="AM33" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-12.335608133036382</v>
       </c>
       <c r="AN33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.6046164305057089E-4</v>
       </c>
       <c r="AO33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.13792780329029952</v>
       </c>
       <c r="AP33" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>2.9653202617369625</v>
       </c>
       <c r="AQ33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-15.301088856416399</v>
       </c>
       <c r="AS33" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.633</v>
       </c>
       <c r="AT33" s="10">
@@ -11941,35 +11939,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW33" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.90410807219577016</v>
       </c>
       <c r="AX33" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ33" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA33" s="10">
+        <f t="shared" si="21"/>
+        <v>0.53580535890547065</v>
+      </c>
+      <c r="BB33" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC33" s="10">
+        <f t="shared" si="23"/>
+        <v>0.13792635684932095</v>
+      </c>
+      <c r="BD33" s="10">
         <f t="shared" si="24"/>
-        <v>0.53580535890547065</v>
-      </c>
-      <c r="BB33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF33" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="10">
-        <f t="shared" si="19"/>
-        <v>0.13792635684932095</v>
-      </c>
-      <c r="BD33" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF33" s="1">
-        <f t="shared" si="21"/>
         <v>1.4464409785475141E-6</v>
       </c>
     </row>
@@ -12076,44 +12074,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI34" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI34">
+        <f t="shared" si="8"/>
         <v>33.240683481624224</v>
       </c>
       <c r="AJ34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17.846543164887237</v>
       </c>
       <c r="AK34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.8413945989520355</v>
       </c>
       <c r="AL34" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.192659199153681E-6</v>
       </c>
       <c r="AM34" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-43.56991304219401</v>
       </c>
       <c r="AN34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4.6511471523909877E-4</v>
       </c>
       <c r="AO34">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.54984387497048148</v>
       </c>
       <c r="AP34" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>17.427753415401952</v>
       </c>
       <c r="AQ34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-60.997201342880722</v>
       </c>
       <c r="AS34" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.7230000000000001</v>
       </c>
       <c r="AT34" s="10">
@@ -12123,35 +12121,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW34" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.86809754131398642</v>
       </c>
       <c r="AX34" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ34" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA34" s="10">
+        <f t="shared" si="21"/>
+        <v>8.7878756343504991E-2</v>
+      </c>
+      <c r="BB34" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC34" s="10">
+        <f t="shared" si="23"/>
+        <v>0.54984806762968064</v>
+      </c>
+      <c r="BD34" s="10">
         <f t="shared" si="24"/>
-        <v>8.7878756343504991E-2</v>
-      </c>
-      <c r="BB34" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF34" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="10">
-        <f t="shared" si="19"/>
-        <v>0.54984806762968064</v>
-      </c>
-      <c r="BD34" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF34" s="1">
-        <f t="shared" si="21"/>
         <v>-4.192659199153681E-6</v>
       </c>
     </row>
@@ -12258,44 +12256,44 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI35" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI35">
+        <f t="shared" si="8"/>
         <v>33.113887057984215</v>
       </c>
       <c r="AJ35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17.778467613766406</v>
       </c>
       <c r="AK35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.83818510339289298</v>
       </c>
       <c r="AL35" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.73174881690219E-6</v>
       </c>
       <c r="AM35" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>-31.175389333595401</v>
       </c>
       <c r="AN35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.9211240875521116E-4</v>
       </c>
       <c r="AO35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.5526148424111158</v>
       </c>
       <c r="AP35" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>30.129402760807796</v>
       </c>
       <c r="AQ35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-61.304599981994436</v>
       </c>
       <c r="AS35" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.736</v>
       </c>
       <c r="AT35" s="10">
@@ -12305,35 +12303,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.8713109817305762</v>
       </c>
       <c r="AX35" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AZ35" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA35" s="10">
+        <f t="shared" si="21"/>
+        <v>8.8321229319460404E-2</v>
+      </c>
+      <c r="BB35" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC35" s="10">
+        <f t="shared" si="23"/>
+        <v>0.55261657415993271</v>
+      </c>
+      <c r="BD35" s="10">
         <f t="shared" si="24"/>
-        <v>8.8321229319460404E-2</v>
-      </c>
-      <c r="BB35" s="10">
+        <v>0</v>
+      </c>
+      <c r="BF35" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC35" s="10">
-        <f t="shared" si="19"/>
-        <v>0.55261657415993271</v>
-      </c>
-      <c r="BD35" s="10">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="BF35" s="1">
-        <f t="shared" si="21"/>
         <v>-1.73174881690219E-6</v>
       </c>
     </row>
@@ -12440,44 +12438,44 @@
         <f t="shared" ref="AH36:AH67" si="33">G36/F36*X36</f>
         <v>0</v>
       </c>
-      <c r="AI36" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI36">
+        <f t="shared" ref="AI36:AI67" si="34">M36/F36/(0.9*8760)</f>
         <v>33.042574535146869</v>
       </c>
       <c r="AJ36">
-        <f t="shared" ref="AJ36:AJ67" si="34">N36/F36/(0.9*8760)</f>
+        <f t="shared" ref="AJ36:AJ67" si="35">N36/F36/(0.9*8760)</f>
         <v>17.740180735046923</v>
       </c>
       <c r="AK36">
-        <f t="shared" ref="AK36:AK67" si="35">O36/F36</f>
+        <f t="shared" ref="AK36:AK67" si="36">O36/F36</f>
         <v>0.83638002704462366</v>
       </c>
       <c r="AL36" s="1">
-        <f t="shared" ref="AL36:AL67" si="36">SUM(AZ36:BD36)-AW36</f>
+        <f t="shared" ref="AL36:AL67" si="37">SUM(AZ36:BD36)-AW36</f>
         <v>-4.6108316680282257E-6</v>
       </c>
       <c r="AM36" s="1">
-        <f t="shared" ref="AM36:AM67" si="37">(Q36+R36)*-1*(I36+K36)/F36</f>
+        <f t="shared" ref="AM36:AM67" si="38">(Q36+R36)*-1*(I36+K36)/F36</f>
         <v>-38.263438157991295</v>
       </c>
       <c r="AN36">
-        <f t="shared" ref="AN36:AN67" si="38">AL36*Q36</f>
+        <f t="shared" ref="AN36:AN67" si="39">AL36*Q36</f>
         <v>-5.1150488423272358E-4</v>
       </c>
       <c r="AO36">
-        <f t="shared" ref="AO36:AO67" si="39">SUM(AZ36:BB36)-AW36</f>
+        <f t="shared" ref="AO36:AO67" si="40">SUM(AZ36:BB36)-AW36</f>
         <v>-0.55272512163114373</v>
       </c>
       <c r="AP36" s="1">
-        <f t="shared" ref="AP36:AP67" si="40">(I36+K36)/F36*-1*R36</f>
+        <f t="shared" ref="AP36:AP67" si="41">(I36+K36)/F36*-1*R36</f>
         <v>23.052884198760367</v>
       </c>
       <c r="AQ36">
-        <f t="shared" ref="AQ36:AQ67" si="41">AO36*Q36</f>
+        <f t="shared" ref="AQ36:AQ67" si="42">AO36*Q36</f>
         <v>-61.316833861635892</v>
       </c>
       <c r="AS36" s="9">
-        <f t="shared" ref="AS36:AS67" si="42">H36</f>
+        <f t="shared" ref="AS36:AS67" si="43">H36</f>
         <v>1.74</v>
       </c>
       <c r="AT36" s="10">
@@ -12487,35 +12485,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW36" s="10">
-        <f t="shared" ref="AW36:AW67" si="43">AS36/F36</f>
+        <f t="shared" ref="AW36:AW67" si="44">AS36/F36</f>
         <v>0.87143787248960791</v>
       </c>
       <c r="AX36" s="10">
-        <f t="shared" ref="AX36:AX67" si="44">AT36*G36/F36</f>
+        <f t="shared" ref="AX36:AX67" si="45">AT36*G36/F36</f>
         <v>0</v>
       </c>
       <c r="AZ36" s="10">
-        <f t="shared" ref="AZ36:AZ67" si="45">AU36</f>
+        <f t="shared" ref="AZ36:AZ67" si="46">AU36</f>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA36" s="10">
-        <f t="shared" ref="BA36:BA67" si="46">J36/F36</f>
+        <f t="shared" ref="BA36:BA67" si="47">J36/F36</f>
         <v>8.833784085846412E-2</v>
       </c>
       <c r="BB36" s="10">
-        <f t="shared" ref="BB36:BB67" si="47">L36/F36</f>
+        <f t="shared" ref="BB36:BB67" si="48">L36/F36</f>
         <v>0</v>
       </c>
       <c r="BC36" s="10">
-        <f t="shared" ref="BC36:BC67" si="48">I36/F36</f>
+        <f t="shared" ref="BC36:BC67" si="49">I36/F36</f>
         <v>0.55272051079947571</v>
       </c>
       <c r="BD36" s="10">
-        <f t="shared" ref="BD36:BD67" si="49">K36/F36</f>
+        <f t="shared" ref="BD36:BD67" si="50">K36/F36</f>
         <v>0</v>
       </c>
       <c r="BF36" s="1">
-        <f t="shared" ref="BF36:BF67" si="50">SUM(AW36:AX36)-SUM(AZ36:BD36)</f>
+        <f t="shared" ref="BF36:BF67" si="51">SUM(AW36:AX36)-SUM(AZ36:BD36)</f>
         <v>4.6108316680282257E-6</v>
       </c>
     </row>
@@ -12622,44 +12620,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI37" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI37">
+        <f t="shared" si="34"/>
         <v>33.296042681972118</v>
       </c>
       <c r="AJ37">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.876264887039209</v>
       </c>
       <c r="AK37">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.84279586172091847</v>
       </c>
       <c r="AL37" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.7053226336892777E-7</v>
       </c>
       <c r="AM37" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-34.706702482590245</v>
       </c>
       <c r="AN37">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.0011630009237841E-5</v>
       </c>
       <c r="AO37">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.54848017784704173</v>
       </c>
       <c r="AP37" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>26.139246459229017</v>
       </c>
       <c r="AQ37">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-60.845918930189249</v>
       </c>
       <c r="AS37" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7170000000000001</v>
       </c>
       <c r="AT37" s="10">
@@ -12669,35 +12667,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.86651526621246533</v>
       </c>
       <c r="AX37" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ37" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA37" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.7660178365423613E-2</v>
       </c>
       <c r="BB37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC37" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.5484804483793051</v>
       </c>
       <c r="BD37" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF37" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-2.7053226336892777E-7</v>
       </c>
     </row>
@@ -12804,44 +12802,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI38" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI38">
+        <f t="shared" si="34"/>
         <v>33.387029287145261</v>
       </c>
       <c r="AJ38">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.925114555775615</v>
       </c>
       <c r="AK38">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.84509893224027122</v>
       </c>
       <c r="AL38" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.3629203223826138E-6</v>
       </c>
       <c r="AM38" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-49.119920864047849</v>
       </c>
       <c r="AN38">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5.9493820988323421E-4</v>
       </c>
       <c r="AO38">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.54921212684095744</v>
       </c>
       <c r="AP38" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>11.807792126842173</v>
       </c>
       <c r="AQ38">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-60.927118052680143</v>
       </c>
       <c r="AS38" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.714</v>
       </c>
       <c r="AT38" s="10">
@@ -12851,35 +12849,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW38" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.86736501189211068</v>
       </c>
       <c r="AX38" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ38" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA38" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.7777975051153229E-2</v>
       </c>
       <c r="BB38" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC38" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.54921748976127982</v>
       </c>
       <c r="BD38" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF38" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-5.3629203223826138E-6</v>
       </c>
     </row>
@@ -12986,44 +12984,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI39" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI39">
+        <f t="shared" si="34"/>
         <v>31.777337720030705</v>
       </c>
       <c r="AJ39">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.06088954516337</v>
       </c>
       <c r="AK39">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.8043541084673923</v>
       </c>
       <c r="AL39" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.954759489053437E-6</v>
       </c>
       <c r="AM39" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-43.558169387751484</v>
       </c>
       <c r="AN39">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-2.1685220761457111E-4</v>
       </c>
       <c r="AO39">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.54970181861157941</v>
       </c>
       <c r="AP39" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>17.423056010713037</v>
       </c>
       <c r="AQ39">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-60.981442250672131</v>
       </c>
       <c r="AS39" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.802</v>
       </c>
       <c r="AT39" s="10">
@@ -13033,35 +13031,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW39" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.86793179847798863</v>
       </c>
       <c r="AX39" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ39" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA39" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.7855069866409258E-2</v>
       </c>
       <c r="BB39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC39" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.54969986385209035</v>
       </c>
       <c r="BD39" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF39" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.954759489053437E-6</v>
       </c>
     </row>
@@ -13168,44 +13166,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI40" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI40">
+        <f t="shared" si="34"/>
         <v>31.877136094278278</v>
       </c>
       <c r="AJ40">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.114470152035651</v>
       </c>
       <c r="AK40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.80688022418708016</v>
       </c>
       <c r="AL40" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.6465955218203376E-6</v>
       </c>
       <c r="AM40" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-31.237608198742397</v>
       </c>
       <c r="AN40">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.8266588598473139E-4</v>
       </c>
       <c r="AO40">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.55371782240680512</v>
       </c>
       <c r="AP40" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>30.189534078728954</v>
       </c>
       <c r="AQ40">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-61.426959611585367</v>
       </c>
       <c r="AS40" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.806</v>
       </c>
       <c r="AT40" s="10">
@@ -13215,35 +13213,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW40" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.87259023046818374</v>
       </c>
       <c r="AX40" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ40" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA40" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.8497498061378604E-2</v>
       </c>
       <c r="BB40" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC40" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.55371946900232694</v>
       </c>
       <c r="BD40" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF40" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-1.6465955218203376E-6</v>
       </c>
     </row>
@@ -13350,44 +13348,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI41" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI41">
+        <f t="shared" si="34"/>
         <v>31.794182725809723</v>
       </c>
       <c r="AJ41">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.069933436300992</v>
       </c>
       <c r="AK41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.80478049250638517</v>
       </c>
       <c r="AL41" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-3.2064230243156189E-6</v>
       </c>
       <c r="AM41" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-38.081713317304633</v>
       </c>
       <c r="AN41">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-3.5570611896900415E-4</v>
       </c>
       <c r="AO41">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.55009867745595964</v>
       </c>
       <c r="AP41" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>22.943398958801268</v>
       </c>
       <c r="AQ41">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-61.025467982224868</v>
       </c>
       <c r="AS41" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.802</v>
       </c>
       <c r="AT41" s="10">
@@ -13397,35 +13395,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW41" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.86839188472844686</v>
       </c>
       <c r="AX41" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ41" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA41" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.7918297272487261E-2</v>
       </c>
       <c r="BB41" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC41" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.55009547103293532</v>
       </c>
       <c r="BD41" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF41" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3.2064230243156189E-6</v>
       </c>
     </row>
@@ -13532,44 +13530,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI42" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI42">
+        <f t="shared" si="34"/>
         <v>31.661439953127818</v>
       </c>
       <c r="AJ42">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>16.998665358320466</v>
       </c>
       <c r="AK42">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.80142048181207404</v>
       </c>
       <c r="AL42" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-4.2853082286020694E-6</v>
       </c>
       <c r="AM42" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-35.108492584445699</v>
       </c>
       <c r="AN42">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-4.7539278099692722E-4</v>
       </c>
       <c r="AO42">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.55483434340140936</v>
       </c>
       <c r="AP42" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>26.441853441339944</v>
       </c>
       <c r="AQ42">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-61.550821418566642</v>
       </c>
       <c r="AS42" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.821</v>
       </c>
       <c r="AT42" s="10">
@@ -13579,35 +13577,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW42" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.87388424992801605</v>
       </c>
       <c r="AX42" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ42" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA42" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>8.8674996526606722E-2</v>
       </c>
       <c r="BB42" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC42" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.55483005809318076</v>
       </c>
       <c r="BD42" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF42" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4.2853082286020694E-6</v>
       </c>
     </row>
@@ -13714,44 +13712,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI43" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI43">
+        <f t="shared" si="34"/>
         <v>32.063035707016454</v>
       </c>
       <c r="AJ43">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.214277530090971</v>
       </c>
       <c r="AK43">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.81158575108130426</v>
       </c>
       <c r="AL43" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.0212833154721324E-6</v>
       </c>
       <c r="AM43" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-50.476878612233527</v>
       </c>
       <c r="AN43">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-1.1329656809457553E-4</v>
       </c>
       <c r="AO43">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.56439086708794828</v>
       </c>
       <c r="AP43" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.133987176297387</v>
       </c>
       <c r="AQ43">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-62.610979085099011</v>
       </c>
       <c r="AS43" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.821</v>
       </c>
       <c r="AT43" s="10">
@@ -13761,35 +13759,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW43" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.88496865432278748</v>
       </c>
       <c r="AX43" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ43" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA43" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.0202877234839232E-2</v>
       </c>
       <c r="BB43" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC43" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.56438984580463281</v>
       </c>
       <c r="BD43" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF43" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.0212833154721324E-6</v>
       </c>
     </row>
@@ -13896,44 +13894,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI44" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI44">
+        <f t="shared" si="34"/>
         <v>35.292665333437341</v>
       </c>
       <c r="AJ44">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>18.94822877590039</v>
       </c>
       <c r="AK44">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.89333475981598376</v>
       </c>
       <c r="AL44" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.1796002730197799E-6</v>
       </c>
       <c r="AM44" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-46.390608762541397</v>
       </c>
       <c r="AN44">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5.7460150983038385E-4</v>
       </c>
       <c r="AO44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.58543979385068723</v>
       </c>
       <c r="AP44" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>18.556017991612787</v>
       </c>
       <c r="AQ44">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-64.946052152644356</v>
       </c>
       <c r="AS44" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7</v>
       </c>
       <c r="AT44" s="10">
@@ -13943,35 +13941,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW44" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.90938268963303737</v>
       </c>
       <c r="AX44" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ44" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA44" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.3567985782350177E-2</v>
       </c>
       <c r="BB44" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC44" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.58544497345096025</v>
       </c>
       <c r="BD44" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF44" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-5.1796002730197799E-6</v>
       </c>
     </row>
@@ -14078,44 +14076,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI45" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI45">
+        <f t="shared" si="34"/>
         <v>35.069424639519347</v>
       </c>
       <c r="AJ45">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>18.828373398005734</v>
       </c>
       <c r="AK45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.88768404826449798</v>
       </c>
       <c r="AL45" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-4.1701444850605895E-6</v>
       </c>
       <c r="AM45" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-32.953967750109001</v>
       </c>
       <c r="AN45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-4.6261703433142759E-4</v>
       </c>
       <c r="AO45">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.58414791789930787</v>
       </c>
       <c r="AP45" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>31.848306889939906</v>
       </c>
       <c r="AQ45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-64.802737257083237</v>
       </c>
       <c r="AS45" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.708</v>
       </c>
       <c r="AT45" s="10">
@@ -14125,35 +14123,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW45" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.90788284696752242</v>
       </c>
       <c r="AX45" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ45" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA45" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.3360019068214534E-2</v>
       </c>
       <c r="BB45" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC45" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.58414374775482281</v>
       </c>
       <c r="BD45" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF45" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4.1701444850605895E-6</v>
       </c>
     </row>
@@ -14260,44 +14258,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI46" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI46">
+        <f t="shared" si="34"/>
         <v>35.028462210951822</v>
       </c>
       <c r="AJ46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>18.806381138130178</v>
       </c>
       <c r="AK46">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.88664719936288827</v>
       </c>
       <c r="AL46" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.4095775353606399E-6</v>
       </c>
       <c r="AM46" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-40.439038096124357</v>
       </c>
       <c r="AN46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-1.5637217880695752E-4</v>
       </c>
       <c r="AO46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.58414875411147693</v>
       </c>
       <c r="AP46" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>24.363635554389315</v>
       </c>
       <c r="AQ46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-64.802830022692461</v>
       </c>
       <c r="AS46" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.71</v>
       </c>
       <c r="AT46" s="10">
@@ -14307,35 +14305,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW46" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.90788425803026285</v>
       </c>
       <c r="AX46" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ46" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA46" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.3360593918785886E-2</v>
       </c>
       <c r="BB46" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC46" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.58414734453394157</v>
       </c>
       <c r="BD46" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF46" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.4095775353606399E-6</v>
       </c>
     </row>
@@ -14442,44 +14440,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI47" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI47">
+        <f t="shared" si="34"/>
         <v>35.170376125767767</v>
       </c>
       <c r="AJ47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>18.88257309753622</v>
       </c>
       <c r="AK47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.89023935177781333</v>
       </c>
       <c r="AL47" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.1814672146170935E-6</v>
       </c>
       <c r="AM47" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-36.553687564641066</v>
       </c>
       <c r="AN47">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.3106664791688407E-4</v>
       </c>
       <c r="AO47">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.57766772716587833</v>
       </c>
       <c r="AP47" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>27.530297605343051</v>
       </c>
       <c r="AQ47">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-64.083854103336208</v>
       </c>
       <c r="AS47" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.6890000000000001</v>
       </c>
       <c r="AT47" s="10">
@@ -14489,35 +14487,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW47" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.90036782344474664</v>
       </c>
       <c r="AX47" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ47" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA47" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.2325186278868279E-2</v>
       </c>
       <c r="BB47" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC47" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.57766890863309295</v>
       </c>
       <c r="BD47" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF47" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-1.1814672146170935E-6</v>
       </c>
     </row>
@@ -14624,44 +14622,44 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AI48" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI48">
+        <f t="shared" si="34"/>
         <v>36.527576444650514</v>
       </c>
       <c r="AJ48">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>19.611238441849292</v>
       </c>
       <c r="AK48">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.92459306832023025</v>
       </c>
       <c r="AL48" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.4464409785475141E-6</v>
       </c>
       <c r="AM48" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-51.952722412582887</v>
       </c>
       <c r="AN48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-1.6046164305057089E-4</v>
       </c>
       <c r="AO48">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.58089293176475987</v>
       </c>
       <c r="AP48" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.488760891313056</v>
       </c>
       <c r="AQ48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-64.441643765538998</v>
       </c>
       <c r="AS48" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.633</v>
       </c>
       <c r="AT48" s="10">
@@ -14671,35 +14669,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW48" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.90410807219577016</v>
       </c>
       <c r="AX48" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AZ48" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA48" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.2840230431010293E-2</v>
       </c>
       <c r="BB48" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="BC48" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.58089148532378132</v>
       </c>
       <c r="BD48" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF48" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.4464409785475141E-6</v>
       </c>
     </row>
@@ -14806,44 +14804,44 @@
         <f t="shared" si="33"/>
         <v>4.4582432500778877</v>
       </c>
-      <c r="AI49" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI49">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK49">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL49" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM49" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN49">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO49">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP49" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ49">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS49" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT49" s="10">
@@ -14853,35 +14851,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW49" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX49" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ49" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA49" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB49" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC49" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD49" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF49" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -14988,44 +14986,44 @@
         <f t="shared" si="33"/>
         <v>4.4588876537174817</v>
       </c>
-      <c r="AI50" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI50">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ50">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK50">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL50" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM50" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN50">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO50">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP50" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ50">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS50" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT50" s="10">
@@ -15035,35 +15033,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW50" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX50" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ50" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA50" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB50" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC50" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD50" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF50" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -15170,44 +15168,44 @@
         <f t="shared" si="33"/>
         <v>4.4588204059212524</v>
       </c>
-      <c r="AI51" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI51">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ51">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL51" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM51" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO51">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP51" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ51">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS51" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT51" s="10">
@@ -15217,35 +15215,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW51" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX51" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ51" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA51" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB51" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC51" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD51" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF51" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -15352,44 +15350,44 @@
         <f t="shared" si="33"/>
         <v>4.3502099918814583</v>
       </c>
-      <c r="AI52" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI52">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ52">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK52">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL52" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM52" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN52">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO52">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP52" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ52">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS52" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT52" s="10">
@@ -15399,35 +15397,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW52" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX52" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ52" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA52" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB52" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC52" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD52" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF52" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -15534,44 +15532,44 @@
         <f t="shared" si="33"/>
         <v>4.3815853326152974</v>
       </c>
-      <c r="AI53" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI53">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ53">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK53">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL53" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM53" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN53">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO53">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP53" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ53">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS53" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT53" s="10">
@@ -15581,35 +15579,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW53" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX53" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ53" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA53" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB53" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC53" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD53" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF53" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -15716,44 +15714,44 @@
         <f t="shared" si="33"/>
         <v>4.381552688054021</v>
       </c>
-      <c r="AI54" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI54">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ54">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK54">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL54" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM54" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN54">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO54">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP54" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ54">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS54" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT54" s="10">
@@ -15763,35 +15761,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW54" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX54" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ54" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA54" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB54" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC54" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD54" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF54" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -15898,44 +15896,44 @@
         <f t="shared" si="33"/>
         <v>4.3815464855873785</v>
       </c>
-      <c r="AI55" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI55">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ55">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK55">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL55" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM55" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN55">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO55">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP55" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ55">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS55" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT55" s="10">
@@ -15945,35 +15943,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW55" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX55" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ55" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA55" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB55" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC55" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD55" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF55" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16080,44 +16078,44 @@
         <f t="shared" si="33"/>
         <v>4.3822320213741799</v>
       </c>
-      <c r="AI56" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI56">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ56">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK56">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL56" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM56" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO56">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP56" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ56">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS56" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT56" s="10">
@@ -16127,35 +16125,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW56" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX56" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ56" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA56" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB56" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC56" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD56" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF56" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16262,44 +16260,44 @@
         <f t="shared" si="33"/>
         <v>4.3821236414307432</v>
       </c>
-      <c r="AI57" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI57">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ57">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.2208724377810398</v>
       </c>
       <c r="AK57">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1853200395467898</v>
       </c>
       <c r="AL57" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM57" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AN57">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO57">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AP57" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AQ57">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AS57" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT57" s="10">
@@ -16309,35 +16307,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW57" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX57" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ57" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA57" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.33620857898883527</v>
       </c>
       <c r="BB57" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC57" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="BD57" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF57" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16444,44 +16442,44 @@
         <f t="shared" si="33"/>
         <v>4.4582432500778877</v>
       </c>
-      <c r="AI58" s="1">
-        <f>M58/F58/(0.9*8760)</f>
+      <c r="AI58">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ58">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK58">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL58" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM58" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-12.034345975279182</v>
       </c>
       <c r="AN58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO58">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP58" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.74785051790335089</v>
       </c>
       <c r="AQ58">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS58" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT58" s="10">
@@ -16491,35 +16489,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW58" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX58" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ58" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA58" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB58" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC58" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD58" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF58" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16626,44 +16624,44 @@
         <f t="shared" si="33"/>
         <v>4.4588876537174817</v>
       </c>
-      <c r="AI59" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI59">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ59">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK59">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL59" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM59" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-11.933266540644022</v>
       </c>
       <c r="AN59">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO59">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP59" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.84892995253851156</v>
       </c>
       <c r="AQ59">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS59" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT59" s="10">
@@ -16673,35 +16671,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW59" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX59" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ59" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA59" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB59" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC59" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD59" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF59" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16808,44 +16806,44 @@
         <f t="shared" si="33"/>
         <v>4.4588204059212524</v>
       </c>
-      <c r="AI60" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI60">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ60">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK60">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL60" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM60" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-10.870540078119028</v>
       </c>
       <c r="AN60">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO60">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP60" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1.9116564150635074</v>
       </c>
       <c r="AQ60">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS60" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT60" s="10">
@@ -16855,35 +16853,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW60" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX60" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ60" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA60" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB60" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC60" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD60" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF60" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -16990,44 +16988,44 @@
         <f t="shared" si="33"/>
         <v>4.3502099918814583</v>
       </c>
-      <c r="AI61" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI61">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ61">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK61">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL61" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM61" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-10.305006529749678</v>
       </c>
       <c r="AN61">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO61">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP61" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.4771899634328549</v>
       </c>
       <c r="AQ61">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS61" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT61" s="10">
@@ -17037,35 +17035,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW61" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX61" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ61" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA61" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB61" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC61" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD61" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF61" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -17172,44 +17170,44 @@
         <f t="shared" si="33"/>
         <v>4.3815853326152974</v>
       </c>
-      <c r="AI62" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI62">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK62">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL62" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM62" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-7.9765185882243035</v>
       </c>
       <c r="AN62">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO62">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP62" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.8056779049582303</v>
       </c>
       <c r="AQ62">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS62" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT62" s="10">
@@ -17219,35 +17217,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW62" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX62" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ62" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA62" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB62" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC62" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD62" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF62" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -17354,44 +17352,44 @@
         <f t="shared" si="33"/>
         <v>4.381552688054021</v>
       </c>
-      <c r="AI63" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI63">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ63">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK63">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL63" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM63" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-9.1301720547515757</v>
       </c>
       <c r="AN63">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO63">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP63" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.6520244384309577</v>
       </c>
       <c r="AQ63">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS63" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT63" s="10">
@@ -17401,35 +17399,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW63" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX63" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ63" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA63" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB63" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC63" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD63" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF63" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -17536,44 +17534,44 @@
         <f t="shared" si="33"/>
         <v>4.3815464855873785</v>
       </c>
-      <c r="AI64" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI64">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ64">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK64">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL64" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM64" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-7.2910012659526497</v>
       </c>
       <c r="AN64">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO64">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP64" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.4911952272298832</v>
       </c>
       <c r="AQ64">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS64" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT64" s="10">
@@ -17583,35 +17581,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW64" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX64" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ64" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA64" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB64" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC64" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD64" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF64" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -17718,44 +17716,44 @@
         <f t="shared" si="33"/>
         <v>4.3822320213741799</v>
       </c>
-      <c r="AI65" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI65">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ65">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK65">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL65" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM65" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-6.5001436037797653</v>
       </c>
       <c r="AN65">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO65">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP65" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.2820528894027676</v>
       </c>
       <c r="AQ65">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS65" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT65" s="10">
@@ -17765,35 +17763,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW65" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX65" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ65" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA65" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB65" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC65" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD65" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF65" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -17900,44 +17898,44 @@
         <f t="shared" si="33"/>
         <v>4.3821236414307432</v>
       </c>
-      <c r="AI66" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI66">
+        <f t="shared" si="34"/>
         <v>1.1219173819252375</v>
       </c>
       <c r="AJ66">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.8355578478551591</v>
       </c>
       <c r="AK66">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1724348446793407</v>
       </c>
       <c r="AL66" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM66" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-5.5407621837927623</v>
       </c>
       <c r="AN66">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO66">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5517974869323083E-2</v>
       </c>
       <c r="AP66" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7.2414343093897706</v>
       </c>
       <c r="AQ66">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-6.1589139124899663</v>
       </c>
       <c r="AS66" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT66" s="10">
@@ -17947,35 +17945,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW66" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX66" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ66" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA66" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB66" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>5.9703910881649988E-2</v>
       </c>
       <c r="BC66" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD66" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="BF66" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18082,44 +18080,44 @@
         <f t="shared" si="33"/>
         <v>4.4582432500778877</v>
       </c>
-      <c r="AI67" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI67">
+        <f t="shared" si="34"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ67">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK67">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL67" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM67" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>-17.178858745136083</v>
       </c>
       <c r="AN67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO67">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP67" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1.0675460416319376</v>
       </c>
       <c r="AQ67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS67" s="20">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT67" s="10">
@@ -18129,35 +18127,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW67" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX67" s="18">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ67" s="18">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA67" s="19">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB67" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC67" s="19">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD67" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF67" s="1">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18229,31 +18227,31 @@
         <v>13.658899</v>
       </c>
       <c r="Z68" t="str">
-        <f t="shared" ref="Z68:Z75" si="51">B68</f>
+        <f t="shared" ref="Z68:Z75" si="52">B68</f>
         <v>NW_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA68" t="str">
-        <f t="shared" ref="AA68:AA75" si="52">C68</f>
+        <f t="shared" ref="AA68:AA75" si="53">C68</f>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB68" s="21">
-        <f t="shared" ref="AB68:AB75" si="53">SUM(AE68:AK68)+AM68+AN68</f>
+        <f t="shared" ref="AB68:AB75" si="54">SUM(AE68:AK68)+AM68+AN68</f>
         <v>48.258880177042066</v>
       </c>
       <c r="AC68" s="21">
-        <f t="shared" ref="AC68:AC75" si="54">SUM(AE68:AK68)+AP68+AQ68</f>
+        <f t="shared" ref="AC68:AC75" si="55">SUM(AE68:AK68)+AP68+AQ68</f>
         <v>48.258880177042073</v>
       </c>
       <c r="AD68" s="5">
-        <f t="shared" ref="AD68:AD75" si="55">AB68-AC68</f>
+        <f t="shared" ref="AD68:AD99" si="56">AB68-AC68</f>
         <v>0</v>
       </c>
       <c r="AE68">
-        <f t="shared" ref="AE68:AE75" si="56">D68/F68*W68*-1</f>
+        <f t="shared" ref="AE68:AE75" si="57">D68/F68*W68*-1</f>
         <v>0</v>
       </c>
       <c r="AF68">
-        <f t="shared" ref="AF68:AF75" si="57">E68/F68*W68</f>
+        <f t="shared" ref="AF68:AF75" si="58">E68/F68*W68</f>
         <v>0.73571231955405192</v>
       </c>
       <c r="AG68" s="1">
@@ -18261,47 +18259,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH68">
-        <f t="shared" ref="AH68:AH75" si="58">G68/F68*X68</f>
+        <f t="shared" ref="AH68:AH75" si="59">G68/F68*X68</f>
         <v>4.4588876537174817</v>
       </c>
-      <c r="AI68" s="1">
-        <f>M68/F68/(0.9*8760)</f>
+      <c r="AI68">
+        <f t="shared" ref="AI68:AI75" si="60">M68/F68/(0.9*8760)</f>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ68">
-        <f t="shared" ref="AJ68:AJ75" si="59">N68/F68/(0.9*8760)</f>
+        <f t="shared" ref="AJ68:AJ75" si="61">N68/F68/(0.9*8760)</f>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK68">
-        <f t="shared" ref="AK68:AK75" si="60">O68/F68</f>
+        <f t="shared" ref="AK68:AK75" si="62">O68/F68</f>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL68" s="1">
-        <f t="shared" ref="AL68:AL75" si="61">SUM(AZ68:BD68)-AW68</f>
+        <f t="shared" ref="AL68:AL75" si="63">SUM(AZ68:BD68)-AW68</f>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM68" s="1">
-        <f t="shared" ref="AM68:AM75" si="62">(Q68+R68)*-1*(I68+K68)/F68</f>
+        <f t="shared" ref="AM68:AM75" si="64">(Q68+R68)*-1*(I68+K68)/F68</f>
         <v>-17.034569281196575</v>
       </c>
       <c r="AN68">
-        <f t="shared" ref="AN68:AN75" si="63">AL68*Q68</f>
+        <f t="shared" ref="AN68:AN75" si="65">AL68*Q68</f>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO68">
-        <f t="shared" ref="AO68:AO75" si="64">SUM(AZ68:BB68)-AW68</f>
+        <f t="shared" ref="AO68:AO75" si="66">SUM(AZ68:BB68)-AW68</f>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP68" s="1">
-        <f t="shared" ref="AP68:AP75" si="65">(I68+K68)/F68*-1*R68</f>
+        <f t="shared" ref="AP68:AP75" si="67">(I68+K68)/F68*-1*R68</f>
         <v>1.2118355055714483</v>
       </c>
       <c r="AQ68">
-        <f t="shared" ref="AQ68:AQ75" si="66">AO68*Q68</f>
+        <f t="shared" ref="AQ68:AQ75" si="68">AO68*Q68</f>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS68" s="20">
-        <f t="shared" ref="AS68:AS75" si="67">H68</f>
+        <f t="shared" ref="AS68:AS75" si="69">H68</f>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT68" s="10">
@@ -18311,35 +18309,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW68" s="18">
-        <f t="shared" ref="AW68:AW75" si="68">AS68/F68</f>
+        <f t="shared" ref="AW68:AW75" si="70">AS68/F68</f>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX68" s="18">
-        <f t="shared" ref="AX68:AX75" si="69">AT68*G68/F68</f>
+        <f t="shared" ref="AX68:AX75" si="71">AT68*G68/F68</f>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ68" s="18">
-        <f t="shared" ref="AZ68:AZ75" si="70">AU68</f>
+        <f t="shared" ref="AZ68:AZ75" si="72">AU68</f>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA68" s="19">
-        <f t="shared" ref="BA68:BA75" si="71">J68/F68</f>
+        <f t="shared" ref="BA68:BA75" si="73">J68/F68</f>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB68" s="18">
-        <f t="shared" ref="BB68:BB75" si="72">L68/F68</f>
+        <f t="shared" ref="BB68:BB75" si="74">L68/F68</f>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC68" s="19">
-        <f t="shared" ref="BC68:BC75" si="73">I68/F68</f>
+        <f t="shared" ref="BC68:BC75" si="75">I68/F68</f>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD68" s="18">
-        <f t="shared" ref="BD68:BD75" si="74">K68/F68</f>
+        <f t="shared" ref="BD68:BD75" si="76">K68/F68</f>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF68" s="1">
-        <f t="shared" ref="BF68:BF75" si="75">SUM(AW68:AX68)-SUM(AZ68:BD68)</f>
+        <f t="shared" ref="BF68:BF75" si="77">SUM(AW68:AX68)-SUM(AZ68:BD68)</f>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18411,31 +18409,31 @@
         <v>13.658693</v>
       </c>
       <c r="Z69" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>SW_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA69" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB69" s="21">
-        <f t="shared" si="53"/>
-        <v>49.810232560601676</v>
-      </c>
-      <c r="AC69" s="21">
         <f t="shared" si="54"/>
         <v>49.810232560601676</v>
       </c>
+      <c r="AC69" s="21">
+        <f t="shared" si="55"/>
+        <v>49.810232560601676</v>
+      </c>
       <c r="AD69" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE69">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF69">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.77010494986327993</v>
       </c>
       <c r="AG69" s="1">
@@ -18443,47 +18441,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH69">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.4588204059212524</v>
       </c>
-      <c r="AI69" s="1">
-        <f t="shared" si="22"/>
+      <c r="AI69">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ69">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL69" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM69" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-15.51754228014997</v>
       </c>
       <c r="AN69">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO69">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP69" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2.7288625066180532</v>
       </c>
       <c r="AQ69">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS69" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT69" s="10">
@@ -18493,35 +18491,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW69" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX69" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ69" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA69" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB69" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC69" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD69" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF69" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18593,31 +18591,31 @@
         <v>13.325987</v>
       </c>
       <c r="Z70" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>TX_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA70" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB70" s="21">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>50.295233423952432</v>
       </c>
       <c r="AC70" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>50.295233423952439</v>
       </c>
       <c r="AD70" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE70">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF70">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.55642508214054021</v>
       </c>
       <c r="AG70" s="1">
@@ -18625,47 +18623,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.3502099918814583</v>
       </c>
-      <c r="AI70" s="1">
-        <f t="shared" ref="AI70:AI75" si="76">M70/F70/(0.9*8760)</f>
+      <c r="AI70">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL70" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM70" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-14.710251135036682</v>
       </c>
       <c r="AN70">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO70">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP70" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3.5361536517313401</v>
       </c>
       <c r="AQ70">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS70" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT70" s="10">
@@ -18675,35 +18673,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW70" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX70" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ70" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA70" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB70" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC70" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD70" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF70" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18775,31 +18773,31 @@
         <v>13.422098999999999</v>
       </c>
       <c r="Z71" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>NCEN_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA71" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB71" s="21">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>53.938865125947238</v>
       </c>
       <c r="AC71" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>53.938865125947245</v>
       </c>
       <c r="AD71" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE71">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF71">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.84479782568051998</v>
       </c>
       <c r="AG71" s="1">
@@ -18807,47 +18805,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH71">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.3815853326152974</v>
       </c>
-      <c r="AI71" s="1">
-        <f t="shared" si="76"/>
+      <c r="AI71">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ71">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK71">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL71" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM71" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-11.386367517315685</v>
       </c>
       <c r="AN71">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO71">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP71" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>6.8600372694523388</v>
       </c>
       <c r="AQ71">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS71" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT71" s="10">
@@ -18857,35 +18855,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW71" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX71" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ71" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA71" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB71" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC71" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD71" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF71" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -18957,31 +18955,31 @@
         <v>13.421999</v>
       </c>
       <c r="Z72" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>CEN_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA72" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB72" s="21">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>52.144709703666216</v>
       </c>
       <c r="AC72" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>52.144709703666223</v>
       </c>
       <c r="AD72" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE72">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF72">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.69749906174759979</v>
       </c>
       <c r="AG72" s="1">
@@ -18989,47 +18987,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH72">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.381552688054021</v>
       </c>
-      <c r="AI72" s="1">
-        <f t="shared" si="76"/>
+      <c r="AI72">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ72">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL72" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM72" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-13.03319153110251</v>
       </c>
       <c r="AN72">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO72">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP72" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>5.2132132556655133</v>
       </c>
       <c r="AQ72">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS72" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT72" s="10">
@@ -19039,35 +19037,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW72" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX72" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ72" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA72" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB72" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC72" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD72" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF72" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -19139,31 +19137,31 @@
         <v>13.42198</v>
       </c>
       <c r="Z73" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>SE_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA73" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB73" s="21">
-        <f t="shared" si="53"/>
-        <v>55.123687040887418</v>
-      </c>
-      <c r="AC73" s="21">
         <f t="shared" si="54"/>
         <v>55.123687040887418</v>
       </c>
+      <c r="AC73" s="21">
+        <f t="shared" si="55"/>
+        <v>55.123687040887418</v>
+      </c>
       <c r="AD73" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE73">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF73">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0510923015505034</v>
       </c>
       <c r="AG73" s="1">
@@ -19171,47 +19169,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH73">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.3815464855873785</v>
       </c>
-      <c r="AI73" s="1">
-        <f t="shared" si="76"/>
+      <c r="AI73">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ73">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK73">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL73" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM73" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-10.407801231217576</v>
       </c>
       <c r="AN73">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO73">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP73" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>7.8386035555504465</v>
       </c>
       <c r="AQ73">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS73" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT73" s="10">
@@ -19221,35 +19219,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW73" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX73" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ73" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA73" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB73" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC73" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD73" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF73" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -19321,31 +19319,31 @@
         <v>13.42408</v>
       </c>
       <c r="Z74" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>MIDAT_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA74" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB74" s="21">
-        <f t="shared" si="53"/>
-        <v>56.28464958619972</v>
-      </c>
-      <c r="AC74" s="21">
         <f t="shared" si="54"/>
         <v>56.28464958619972</v>
       </c>
+      <c r="AC74" s="21">
+        <f t="shared" si="55"/>
+        <v>56.28464958619972</v>
+      </c>
       <c r="AD74" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE74">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF74">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.0824311790092787</v>
       </c>
       <c r="AG74" s="1">
@@ -19353,47 +19351,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH74">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.3822320213741799</v>
       </c>
-      <c r="AI74" s="1">
-        <f t="shared" si="76"/>
+      <c r="AI74">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ74">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK74">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL74" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM74" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-9.2788630991508381</v>
       </c>
       <c r="AN74">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO74">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP74" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>8.9675416876171834</v>
       </c>
       <c r="AQ74">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS74" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT74" s="10">
@@ -19403,35 +19401,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW74" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX74" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ74" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA74" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB74" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC74" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD74" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF74" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
@@ -19503,31 +19501,31 @@
         <v>13.423748</v>
       </c>
       <c r="Z75" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>NE_DryMill_CCS_Fermentation_Exhaust</v>
       </c>
       <c r="AA75" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>Biomass_Corn</v>
       </c>
       <c r="AB75" s="21">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>57.876992578251155</v>
       </c>
       <c r="AC75" s="21">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>57.876992578251162</v>
       </c>
       <c r="AD75" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE75">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF75">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.3053791371484904</v>
       </c>
       <c r="AG75" s="1">
@@ -19535,47 +19533,47 @@
         <v>51.540779469794813</v>
       </c>
       <c r="AH75">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.3821236414307432</v>
       </c>
-      <c r="AI75" s="1">
-        <f t="shared" si="76"/>
+      <c r="AI75">
+        <f t="shared" si="60"/>
         <v>1.8459716853700829</v>
       </c>
       <c r="AJ75">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>8.2322589053372308</v>
       </c>
       <c r="AK75">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-8.1434431562275815</v>
       </c>
       <c r="AL75" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5.9703909015778822E-2</v>
       </c>
       <c r="AM75" s="1">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-7.9093596852951915</v>
       </c>
       <c r="AN75">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>6.6232825806925684</v>
       </c>
       <c r="AO75">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-0.10477370129031155</v>
       </c>
       <c r="AP75" s="1">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>10.33704510147283</v>
       </c>
       <c r="AQ75">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-11.623122206075447</v>
       </c>
       <c r="AS75" s="20">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>1.7588666580000001</v>
       </c>
       <c r="AT75" s="10">
@@ -19585,35 +19583,35 @@
         <v>0.23037490999999999</v>
       </c>
       <c r="AW75" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0.56658349085470638</v>
       </c>
       <c r="AX75" s="18">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5.9703910798172485E-2</v>
       </c>
       <c r="AZ75" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.23037490999999999</v>
       </c>
       <c r="BA75" s="19">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.22098669510373337</v>
       </c>
       <c r="BB75" s="18">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>1.0448184460661475E-2</v>
       </c>
       <c r="BC75" s="19">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>0.11522188388510189</v>
       </c>
       <c r="BD75" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>4.9255726420988515E-2</v>
       </c>
       <c r="BF75" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>1.7823936770966498E-9</v>
       </c>
     </row>
